--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure ETL Architect – Data Modernization</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,139 +591,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
+          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
+          <t>Azure ETL Architect – Data Modernization</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks/AWS)</t>
+          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Data Engineer (Databricks/AWS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SambaSafety</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
+          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>SambaSafety</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aivanta Tech Inc</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Michigan, ND, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aivanta Tech Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Michigan, ND, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658f836c897914f9</t>
+          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
+          <t>https://www.indeed.com/viewjob?jk=658f836c897914f9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alliance Laundry</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer IV. 4P/796</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Alliance Laundry</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
+          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Full stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,15 +1318,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Software Engineer - Full stack</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer Consultant - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef1687719f12bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Power BI Developer – Data Modernization</t>
+          <t>Sr Data Engineer Consultant - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=eef1687719f12bcd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Power BI Developer – Data Modernization</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI/ML ENG III</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI/ML ENG III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Virtual</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Data Engineer 3 - Virtual</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Power BI, Tableau, MLOps, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
+          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Engineer I</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Full Stack Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Power BI, Tableau, MLOps, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Specialist, AI Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Acquisition Engineer I</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - On-Site (Texas)</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Southside Bank</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Specialist, AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Bedford, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Acquisition Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer III 4P/797</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,472 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - HYBRID</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sr Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Authority Brands</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; BI Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Allen Park, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ketch</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Monogram Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI/ML ENG III</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,94 +1861,94 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer 3 - Virtual</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Virtual</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Full Stack Engineer I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer I</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Power BI, Tableau, MLOps, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Power BI, Tableau, MLOps, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Specialist, AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bedford, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Data Acquisition Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Specialist, AI Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Acquisition Engineer I</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Sr Integration Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data &amp; BI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ketch</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3435,76 +3435,6 @@
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Ketch</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Monogram Health</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI / Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Celebration, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1d158814d4803d</t>
+          <t>https://www.indeed.com/viewjob?jk=90241e81bace0969</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Senior AI / Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Databricks</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b179b1cd108b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1d158814d4803d</t>
         </is>
       </c>
     </row>
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
+          <t>https://www.indeed.com/viewjob?jk=93b179b1cd108b7b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Senior AI Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Ashra Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,81 +587,81 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, S3, RDS, Azure, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a696b44fd5d4a9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure ETL Architect – Data Modernization</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
+          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks/AWS)</t>
+          <t>Azure ETL Architect – Data Modernization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SambaSafety</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
+          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer (Databricks/AWS)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>SambaSafety</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aivanta Tech Inc</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michigan, ND, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658f836c897914f9</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aivanta Tech Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Michigan, ND, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
+          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,104 +1116,104 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=658f836c897914f9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alliance Laundry</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Alliance Laundry</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Full stack</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
@@ -1383,20 +1383,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer Consultant - Remote</t>
+          <t>Sr Software Engineer - Full stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
+          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef1687719f12bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Power BI Developer – Data Modernization</t>
+          <t>Sr Data Engineer Consultant - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Power BI Developer – Data Modernization</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Storden, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Virtual</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Engineer I</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Full Stack Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Power BI, Tableau, MLOps, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Power BI, Tableau, MLOps, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
         </is>
       </c>
     </row>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Specialist, AI Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, ETL, ELT, CI/CD</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Acquisition Engineer I</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
@@ -2643,20 +2643,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Data Acquisition Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Specialist, AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bedford, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Sr Integration Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data &amp; BI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,42 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -1168,52 +1168,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Alliance Laundry</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alliance Laundry</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Software Engineer - Full stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Full stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Data Engineer Consultant - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Data Engineer Consultant - Remote</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Power BI Developer – Data Modernization</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Power BI Developer – Data Modernization</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Storden, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Storden, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer I</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Full Stack Engineer I</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Power BI, Tableau, MLOps, Azure DevOps</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Specialist, AI Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Entegris</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bedford, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Sr Integration Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data &amp; BI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer I</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Full Stack Engineer I</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,42 +2386,42 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Acquisition Engineer I</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Data Acquisition Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Sr Integration Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,260 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; BI Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Monogram Health</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Acquisition Engineer I</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Data Acquisition Engineer I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Sr Integration Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect</t>
+          <t>Senior Data &amp; BI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Monogram Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,50 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Monogram Health</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,122 +678,122 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure ETL Architect – Data Modernization</t>
+          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
+          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
+          <t>Data Engineer (Databricks/AWS)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
+          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks/AWS)</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>SambaSafety</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SambaSafety</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
+          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Aivanta Tech Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Michigan, ND, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aivanta Tech Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Michigan, ND, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=658f836c897914f9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658f836c897914f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Alliance Laundry</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alliance Laundry</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Software Engineer - Full stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Full stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Data Engineer Consultant - Remote</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer Consultant - Remote</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Storden, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Power BI Developer – Data Modernization</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Storden, MN, US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,94 +2036,94 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Full Stack Engineer I</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer I</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,42 +2386,42 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Data Acquisition Engineer I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,42 +2866,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Acquisition Engineer I</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
@@ -2923,20 +2923,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr Integration Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data &amp; BI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3680,76 +3680,6 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Monogram Health</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI / Data Engineer</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Celebration, FL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1d158814d4803d</t>
+          <t>https://www.indeed.com/viewjob?jk=93b179b1cd108b7b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Senior AI Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Ashra Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Databricks</t>
+          <t>AWS, Glue, S3, RDS, Azure, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b179b1cd108b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a696b44fd5d4a9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer/Data Scientist</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ashra Technologies Pvt Ltd</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a696b44fd5d4a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Data Engineer (Databricks/AWS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>SambaSafety</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark</t>
+          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks/AWS)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SambaSafety</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Aivanta Tech Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Michigan, ND, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aivanta Tech Inc</t>
+          <t>Alliance Laundry</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Michigan, ND, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=658f836c897914f9</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alliance Laundry</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Sr Software Engineer - Full stack</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer Consultant - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Full stack</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Architect - Onsite in Irvine, CA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Data Engineer Consultant - Remote</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Storden, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
+          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Storden, MN, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,77 +1721,77 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,94 +1966,94 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer I</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,42 +2316,42 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>Data Acquisition Engineer I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Acquisition Engineer I</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
@@ -2853,20 +2853,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr Integration Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Authority Brands</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data &amp; BI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,147 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; BI Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Monogram Health</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,52 +678,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Azure Data Architect with Healthcare Payer Exp.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SambaSafety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
+          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>SambaSafety</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aivanta Tech Inc</t>
+          <t>Alliance Laundry</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Michigan, ND, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alliance Laundry</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer - Full stack</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Full stack</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer Consultant - Remote</t>
+          <t>Sr Architect - Onsite in Irvine, CA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Storden, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Architect - Onsite in Irvine, CA</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Storden, MN, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,94 +1616,94 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer I</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Acquisition Engineer I</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AAA Washington</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Integration Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Authority Brands</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7ef087d7f34af1</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data &amp; BI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3470,76 +3470,6 @@
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>DriveTime Automotive Group</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; BI Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alliance Laundry</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Alliance Laundry</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Full stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Machine Learning Architect 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=08d5fa709c2abfb2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=b22e167e69bdfe92</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Machine Learning Architect 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=d2689a7adb5339b8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Architect - Onsite in Irvine, CA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Storden, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>Sr Architect - Onsite in Irvine, CA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Storden, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce8f8f2a4ca6b4b4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,129 +1616,129 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,77 +1991,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Sr. Business Intelligence Developer - REMOTE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Designer Brands Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,54 +2841,54 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2897,11 +2897,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,190 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; BI Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SambaSafety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>SambaSafety</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alliance Laundry</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Architect 2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d5fa709c2abfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22e167e69bdfe92</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Architect 2</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2689a7adb5339b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Machine Learning Architect 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=08d5fa709c2abfb2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=b22e167e69bdfe92</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Architect - Onsite in Irvine, CA</t>
+          <t>Machine Learning Architect 2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d2689a7adb5339b8</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Sr Architect - Onsite in Irvine, CA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8f8f2a4ca6b4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce8f8f2a4ca6b4b4</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,112 +2166,112 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer - REMOTE</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Designer Brands Inc.</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr. Business Intelligence Developer - REMOTE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Designer Brands Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3037,11 +3037,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer II</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IceKredit</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,120 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; BI Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,15 +1353,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Architect 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d5fa709c2abfb2</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22e167e69bdfe92</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Architect 2</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2689a7adb5339b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Storden, MN, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Spark, PySpark, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82dfb61792cd2985</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8f8f2a4ca6b4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>AI TEVV Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Ursa Space Systems</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Python Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>K12 Plus Solutions</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Angelo, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
@@ -2253,52 +2253,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Sr. Business Intelligence Developer - REMOTE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Designer Brands Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer - REMOTE</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Designer Brands Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,15 +3741,190 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; BI Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Senior AI Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Ashra Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Databricks</t>
+          <t>AWS, Glue, S3, RDS, Azure, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93b179b1cd108b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a696b44fd5d4a9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer/Data Scientist</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ashra Technologies Pvt Ltd</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a696b44fd5d4a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
         </is>
       </c>
     </row>
@@ -748,52 +748,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SambaSafety</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>SambaSafety</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,94 +1126,94 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,29 +1361,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,116 +1392,116 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>AWS Cloud Architect (Java Microservices)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Architect - Onsite in Irvine, CA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI TEVV Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Polars, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,164 +1686,164 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d2ca0ad3d344bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Architect - Onsite in Irvine, CA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,112 +2236,112 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>DevOps Engineer II - AWS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer - REMOTE</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Designer Brands Inc.</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Business Intelligence Developer - REMOTE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Designer Brands Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,59 +3366,59 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data &amp; BI Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,322 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - HYBRID</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - HYBRID</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - HYBRID</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DriveTime Automotive Group</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure DBX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks/AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Architect with Healthcare Payer Exp.</t>
+          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>Data Engineer (Databricks/AWS)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - I&amp;D</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
+          <t>https://www.indeed.com/viewjob?jk=812c613e05e7cfce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Azure Data Architect with Healthcare Payer Exp.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SambaSafety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
+          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect (Java Microservices)</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7730389a6a7d162d</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
@@ -1558,20 +1558,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c83954e5f77f972</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Data Analyst 3, Supply Chain Intelligence - (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=33c11ff9d6efa16d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Atrium Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
         </is>
       </c>
     </row>
@@ -2673,52 +2673,52 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer II - AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee27abf4c5229db</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Platform Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Sr. Business Intelligence Developer - REMOTE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Designer Brands Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer - REMOTE</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Designer Brands Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,69 +3356,69 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>System Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
+          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a79b4f16db1d96c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Azure DBX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure DBX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
+          <t>Data Engineer (Databricks/AWS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks/AWS)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=812c613e05e7cfce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Azure Data Architect with Healthcare Payer Exp.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812c613e05e7cfce</t>
+          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Data Architect with Healthcare Payer Exp.</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - I&amp;D</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Customer Experience Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=defc1aca4d641884</t>
         </is>
       </c>
     </row>
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Synectics for Management Decisions Inc</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Architect - Onsite in Irvine, CA</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Facets NetworX Pricing Configuration</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9c395d3ffba8c0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Sr Architect - Onsite in Irvine, CA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analyst 3, Supply Chain Intelligence - (Hybrid - Seattle, WA)</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c11ff9d6efa16d</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Data Analyst 3, Supply Chain Intelligence - (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=33c11ff9d6efa16d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,77 +2341,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb347d2cd6809503</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Redwood Logistics</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93e010ce4c6a9aa0</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer - REMOTE</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Designer Brands Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Sr. Business Intelligence Developer - REMOTE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Designer Brands Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Product Owner</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jack Link's Protein Snacks</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,42 +3356,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>System Software Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3377a7c65bdc0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer III</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,42 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Applied AI Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Changeis, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90241e81bace0969</t>
+          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer/Data Scientist</t>
+          <t>Azure DBX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ashra Technologies Pvt Ltd</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a696b44fd5d4a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Changeis, Inc.</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6794a3834a8cb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure DBX</t>
+          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8699eca260e46b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Databricks/AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c780bb7cb6c4cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Data Platform Engineering</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a33763b20c7bc7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=812c613e05e7cfce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks/AWS)</t>
+          <t>Azure Data Architect with Healthcare Payer Exp.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de00d1a1e6d38ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Solution Architect - I&amp;D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812c613e05e7cfce</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Data Architect with Healthcare Payer Exp.</t>
+          <t>Senior Data Engineer — GCP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c9b744dd583ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Solution Architect - I&amp;D</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Franklin Lakes, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed54c8ce6b401fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — GCP</t>
+          <t>Python Backend Developer - Hybrid/Onsite</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84280e7ee9940e</t>
+          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Data Dimensions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Janesville, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c936dad5028f127</t>
+          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Backend Developer - Hybrid/Onsite</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4f0429ae4593f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data Dimensions</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Janesville, WI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SNS, ECS, IAM, RDS, MySQL, MongoDB, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577e50312f05eeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,112 +976,112 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be59ba9f664cdc8</t>
+          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Downtown Music</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc4bc36aa6fe1e</t>
+          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - Finance Technology Platform (PySpark, Hadoop, Cloud)</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, S3, RDS, Azure, Databricks, GCP, BigQuery, Hadoop</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27ca6662829a272</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>External SambaNova Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798a5f2afe52ecba</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Data Engineer (Python)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hyundai AutoEver America</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6beb523d3112f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Downtown Music</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62178bde1110ca99</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4080c35e50a786</t>
+          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Customer Experience Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24bc0c26ef1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=defc1aca4d641884</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python)</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hyundai AutoEver America</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e9633068d7dbbc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Customer Experience Analyst</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defc1aca4d641884</t>
+          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Resident Solutions Architect (RSA) - Databricks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>TISTA Science and Technology Corporation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Machine Learning Architect II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3baaefe539df3d2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891599544d1068a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect (RSA) - Databricks</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TISTA Science and Technology Corporation</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, ELT, Power BI</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c1e172b887f0e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>PureMagic Carwash</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f867d1be9fe0f69</t>
+          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Sr Architect - Onsite in Irvine, CA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Dataflix</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Zookeeper, Scala, Kafka, Kafka Connect, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd9d834b65f070a</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e16af2f20d1627</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PureMagic Carwash</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alcoa, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e59c05554094978</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Facets NetworX Pricing Configuration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9c395d3ffba8c0</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Architect - Onsite in Irvine, CA</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dataflix</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb4d56aa60d66cf</t>
+          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296a330a7d75e5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,77 +2341,77 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2661,29 +2661,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,77 +2691,77 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>AEP/CDP Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Sr. Business Intelligence Developer - REMOTE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Designer Brands Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AEP/CDP Architect</t>
+          <t>Sr. Java Backend Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba331119c93e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer - REMOTE</t>
+          <t>Sr. Java Backend Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Designer Brands Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Dimension Tables, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bc7ffb6f944b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0477feeb79dcb21</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df9db8529425cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Java Backend Developer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9faee137e1dd64</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Quality Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Quality Engineer - Hybrid On-Site</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,29 +3321,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Oracle, PostgreSQL, ETL, ELT, CI/CD, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0097b274babd6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3352,11 +3352,11 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4135,146 +4135,6 @@
         </is>
       </c>
       <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>

--- a/results/job_matches_2026-08-07.xlsx
+++ b/results/job_matches_2026-08-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technical Architect 8</t>
+          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Technical Architect 8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
+          <t>AWS, Redshift, API Gateway, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
+          <t>https://www.indeed.com/viewjob?jk=7012fb40a43e1d5a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer, Backend - Consumer Experience Platform (Remote, US)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, ECS, RDS, GCP, Scala, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f512c971fe8b64d7</t>
+          <t>https://www.indeed.com/viewjob?jk=41ca370618b5121e</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Customer Experience Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=defc1aca4d641884</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Customer Experience Analyst</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defc1aca4d641884</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fce6d2f8036b7f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior IT Software Engineer – Scala, Akka &amp; Java Microservices</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0861862c8ae6a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=bebe922d1a22e0b2</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II-Hybrid Role</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magid Glove &amp; Safety</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Greenwich, CT, US USA</t>
+          <t>Romeoville, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer</t>
+          <t>Software Engineer II-Hybrid Role</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenwich, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2d1082065c54ae</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Full Stack Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Magid Glove &amp; Safety</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romeoville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae4852afc375b2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5e7ece7dccd02c</t>
         </is>
       </c>
     </row>
@@ -1833,52 +1833,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CDP System Developer (Customer Data Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Avantor</t>
+          <t>Colorado Rockies Baseball Club</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
+          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Colorado Rockies Baseball Club</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c79854ae69714</t>
+          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33567ff533f2727c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8f7d2b652cdd63</t>
+          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d548f0655d8ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III Python Backend/ Pyspark/ Databricks</t>
+          <t>Backend Python/Databricks Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb01818b8a1f0db</t>
+          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Backend Python/Databricks Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=765db6d7bf793609</t>
+          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Consulting Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0882c7b287b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ARC-One Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Consulting Engineer</t>
+          <t>Data Analyst 3, Supply Chain Intelligence - (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, HBase, Scala, Snowflake, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, BigQuery, Dataflow, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e01bb16e952f25f</t>
+          <t>https://www.indeed.com/viewjob?jk=33c11ff9d6efa16d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Full Stack Python Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst 3, Supply Chain Intelligence - (Hybrid - Seattle, WA)</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c11ff9d6efa16d</t>
+          <t>https://www.indeed.com/viewjob?jk=0da9fa927be823d4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ARC-One Solutions</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, Kafka, PostgreSQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00f9372e966a21f</t>
+          <t>https://www.indeed.com/viewjob?jk=50b26690dd93322b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Python Developer - Software Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,69 +2306,69 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a83616a78417328</t>
+          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4198cfd74b483959</t>
+          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9d41ca9c771490</t>
+          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Oracle Data Engineer - Onsite</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7071c457b704b3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833fe86368c4972f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Oracle Data Engineer - Onsite</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, Dimensional Modeling, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e93cd18fa341dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c803152f342224</t>
+          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Business Intelligence &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>County Materials Family of Companies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Westmont, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18b9c3aa39890d54</t>
+          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence &amp; Data Analyst</t>
+          <t>Business Intelligence &amp; Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>County Materials Family of Companies</t>
+          <t>International Scripture Ministries</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038de0d211702e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,94 +2631,94 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461848762436fae0</t>
+          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Intelligence &amp; Data Analytics Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>International Scripture Ministries</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Des Plaines, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80165dd426dcee54</t>
+          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, Splunk, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a855df409a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Des Plaines, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, MongoDB, Data Modeling, Power BI, Git</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=183c1e594d877a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
         </is>
       </c>
     </row>
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551854289f030c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Data Engineer, Data Products</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1920adfde937049c</t>
+          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure &amp; Platform Engineer</t>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4988f99037c8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Data Products</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>National Trench Safety</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, BigQuery, Spark, Scala, Snowflake, MySQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ab2e0926b23cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Billtrust</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed8e38cc4227200</t>
+          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>BI &amp; Analytics Analyst/Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>National Trench Safety</t>
+          <t>Jewish Council for the Aging of Greater Washington</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf80265e943322ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Billtrust</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78178f6aa10eb4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BI &amp; Analytics Analyst/Data Engineer</t>
+          <t>Risk-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jewish Council for the Aging of Greater Washington</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Synapse Analytics, Scala, SQL Server, Kimball, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e88e37f4395eea</t>
+          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63632248996e4946</t>
+          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Risk-Dallas-Associate-Software Engineering</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3568db794bb43c20</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033a483ab033f139</t>
+          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Data Engineer III/Senior (Analytics)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Expeditors</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Ellenwood, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01033a0167d6836</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Romulus, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dacfe71dcf8baca8</t>
+          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ellenwood, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac9200c4cfa508d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer III/Senior (Analytics)</t>
+          <t>Data Engineer - Hybrid On-Site</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Expeditors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romulus, MI, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Power BI, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e659a4bfd0be22cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>26-117: Fire Weather Testbed Cloud Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colorado State University</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce725dc0522c974</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid On-Site</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Scala, Informatica PowerCenter, Oracle, ETL, Jenkins, Jenkins, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6a2f7452936264</t>
+          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>26-117: Fire Weather Testbed Cloud Developer</t>
+          <t>Business Efficiency Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Colorado State University</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b194d8c0cab372</t>
+          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer - (Coalesce, Snowflake)</t>
+          <t>Cloud Data Solutions Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Streams/Tasks</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529cf1fbc3547cd8</t>
+          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7339cfd332732e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer - Streaming</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Scala, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffac0ed2e6c03b03</t>
+          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Streaming</t>
+          <t>AI/ML Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Avilamb</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Event Hubs, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd1f06fd310d8388</t>
+          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI/ML Architect</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Avilamb</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ETL, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d406fc8aace70fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48dcbf107ebdc2d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Business Efficiency Engineer</t>
+          <t>Senior Software Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca3a193745fe7be</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=368b8ec957001455</t>
+          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a24551da2a5d119</t>
+          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4c2485dd3b69b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - HYBRID</t>
+          <t>Applied AI Software Engineer III</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e11b943eb2423bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4030,111 +4030,6 @@
         </is>
       </c>
       <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=803c5841ca815740</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f69a9084f7cc98</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d49b4a7fe8e3ba1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Applied AI Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9b7b08359f538c30</t>
         </is>
